--- a/generated/updated_trim.xlsx
+++ b/generated/updated_trim.xlsx
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C6" s="18" t="n">
-        <v>176</v>
+        <v>202.9</v>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="G6" s="18" t="n">
-        <v>6864</v>
+        <v>7913.1</v>
       </c>
     </row>
     <row r="7">
@@ -939,7 +939,7 @@
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="28" t="n"/>
       <c r="E11" s="20" t="n">
-        <v>48527.52</v>
+        <v>49576.62</v>
       </c>
       <c r="F11" s="5" t="n"/>
       <c r="G11" s="29" t="n"/>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="E13" s="33" t="n">
-        <v>52951.52</v>
+        <v>54000.62</v>
       </c>
       <c r="F13" s="34" t="n"/>
       <c r="G13" s="35" t="n"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B18" s="18" t="n">
-        <v>1470.96</v>
+        <v>1497.86</v>
       </c>
       <c r="C18" s="27" t="n"/>
       <c r="D18" s="27" t="n"/>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B20" s="28" t="n"/>
       <c r="C20" s="1" t="n">
-        <v>1581.56</v>
+        <v>1608.46</v>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B21" s="28" t="n"/>
       <c r="C21" s="1" t="n">
-        <v>33.48</v>
+        <v>33.57</v>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
